--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Voyager - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227D117C-D8C9-4948-9CCB-0D989F2C3D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBBE96E-5E7B-4616-9C0A-91517717AC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Voyager - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBBE96E-5E7B-4616-9C0A-91517717AC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073291F5-8A1F-485E-B63A-294614481CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5897" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6078" uniqueCount="127">
   <si>
     <t>Company Name</t>
   </si>
@@ -417,6 +417,9 @@
   </si>
   <si>
     <t>REVELES ROBERT</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
   </si>
 </sst>
 </file>
@@ -35047,154 +35050,1061 @@
       </c>
     </row>
     <row r="1242" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1242" s="2"/>
-      <c r="I1242" s="1"/>
+      <c r="B1242" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1242">
+        <v>3326</v>
+      </c>
+      <c r="D1242" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1242" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1242" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1242" s="2">
+        <v>3.6921296296296298E-3</v>
+      </c>
+      <c r="I1242" s="1">
+        <v>46118.842361111114</v>
+      </c>
+      <c r="J1242">
+        <v>1</v>
+      </c>
+      <c r="K1242" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1243" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1243" s="2"/>
-      <c r="I1243" s="1"/>
+      <c r="B1243" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1243">
+        <v>1256</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1243" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1243" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1243" s="2">
+        <v>1.4085648148148147E-2</v>
+      </c>
+      <c r="I1243" s="1">
+        <v>46118.843055555553</v>
+      </c>
+      <c r="J1243">
+        <v>1</v>
+      </c>
+      <c r="K1243" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1244" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1244" s="2"/>
-      <c r="I1244" s="1"/>
+      <c r="B1244" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1244">
+        <v>3528</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1244" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1244" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1244" s="2">
+        <v>9.5370370370370366E-3</v>
+      </c>
+      <c r="I1244" s="1">
+        <v>46118.843055555553</v>
+      </c>
+      <c r="J1244">
+        <v>1</v>
+      </c>
+      <c r="K1244" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1245" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1245" s="2"/>
-      <c r="I1245" s="1"/>
+      <c r="B1245" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1245">
+        <v>1751</v>
+      </c>
+      <c r="D1245" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1245" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1245" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1245" s="2">
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="I1245" s="1">
+        <v>46118.84375</v>
+      </c>
+      <c r="J1245">
+        <v>1</v>
+      </c>
+      <c r="K1245" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1246" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1246" s="2"/>
-      <c r="I1246" s="1"/>
+      <c r="B1246" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1246">
+        <v>1278</v>
+      </c>
+      <c r="D1246" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1246" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1246" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1246" s="2">
+        <v>8.2754629629629636E-3</v>
+      </c>
+      <c r="I1246" s="1">
+        <v>46118.84375</v>
+      </c>
+      <c r="J1246">
+        <v>1</v>
+      </c>
+      <c r="K1246" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1247" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1247" s="2"/>
-      <c r="I1247" s="1"/>
+      <c r="B1247" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1247">
+        <v>1262</v>
+      </c>
+      <c r="D1247" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1247" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1247" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1247" s="2">
+        <v>2.9513888888888888E-3</v>
+      </c>
+      <c r="I1247" s="1">
+        <v>46118.844444444447</v>
+      </c>
+      <c r="J1247">
+        <v>1</v>
+      </c>
+      <c r="K1247" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1248" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="I1248" s="1"/>
-    </row>
-    <row r="1249" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1249" s="2"/>
-      <c r="I1249" s="1"/>
-    </row>
-    <row r="1250" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1250" s="2"/>
-      <c r="I1250" s="1"/>
-    </row>
-    <row r="1251" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1251" s="2"/>
-      <c r="I1251" s="1"/>
-    </row>
-    <row r="1252" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1252" s="2"/>
-      <c r="I1252" s="1"/>
-    </row>
-    <row r="1253" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1253" s="2"/>
-      <c r="I1253" s="1"/>
-    </row>
-    <row r="1254" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1254" s="2"/>
-      <c r="I1254" s="1"/>
-    </row>
-    <row r="1255" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1255" s="2"/>
-      <c r="I1255" s="1"/>
-    </row>
-    <row r="1256" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B1248" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1248">
+        <v>1276</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1248" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1248" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1248" s="2">
+        <v>5.2777777777777779E-3</v>
+      </c>
+      <c r="I1248" s="1">
+        <v>46118.845138888886</v>
+      </c>
+      <c r="J1248">
+        <v>1</v>
+      </c>
+      <c r="K1248" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1249" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1249" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1249">
+        <v>2917</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1249" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1249" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1249" s="2">
+        <v>8.2291666666666659E-3</v>
+      </c>
+      <c r="I1249" s="1">
+        <v>46118.845138888886</v>
+      </c>
+      <c r="J1249">
+        <v>1</v>
+      </c>
+      <c r="K1249" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1250" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1250" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1250">
+        <v>1250</v>
+      </c>
+      <c r="D1250" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1250" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1250" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1250" s="2">
+        <v>8.7847222222222215E-3</v>
+      </c>
+      <c r="I1250" s="1">
+        <v>46118.845833333333</v>
+      </c>
+      <c r="J1250">
+        <v>0</v>
+      </c>
+      <c r="K1250" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1251" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1251" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1251">
+        <v>3294</v>
+      </c>
+      <c r="D1251" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1251" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1251" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1251" s="2">
+        <v>8.9467592592592585E-3</v>
+      </c>
+      <c r="I1251" s="1">
+        <v>46118.845833333333</v>
+      </c>
+      <c r="J1251">
+        <v>1</v>
+      </c>
+      <c r="K1251" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1252" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1252" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1252">
+        <v>1762</v>
+      </c>
+      <c r="D1252" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1252" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1252" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1252" s="2">
+        <v>2.2326388888888889E-2</v>
+      </c>
+      <c r="I1252" s="1">
+        <v>46118.84652777778</v>
+      </c>
+      <c r="J1252">
+        <v>1</v>
+      </c>
+      <c r="K1252" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1253" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1253" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1253">
+        <v>2936</v>
+      </c>
+      <c r="D1253" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1253" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1253" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1253" s="2">
+        <v>1.1273148148148148E-2</v>
+      </c>
+      <c r="I1253" s="1">
+        <v>46118.847222222219</v>
+      </c>
+      <c r="J1253">
+        <v>1</v>
+      </c>
+      <c r="K1253" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1254" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1254" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1254">
+        <v>1272</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1254" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1254" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1254" s="2">
+        <v>1.6215277777777776E-2</v>
+      </c>
+      <c r="I1254" s="1">
+        <v>46118.847222222219</v>
+      </c>
+      <c r="J1254">
+        <v>1</v>
+      </c>
+      <c r="K1254" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1255" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1255" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1255">
+        <v>1257</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1255" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1255" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1255" s="2">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="I1255" s="1">
+        <v>46118.847916666666</v>
+      </c>
+      <c r="J1255">
+        <v>0</v>
+      </c>
+      <c r="K1255" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1256" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
-    </row>
-    <row r="1257" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1257" s="2"/>
-      <c r="I1257" s="1"/>
-    </row>
-    <row r="1258" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1258" s="1"/>
-    </row>
-    <row r="1259" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1259" s="2"/>
-      <c r="I1259" s="1"/>
-    </row>
-    <row r="1260" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1260" s="2"/>
-      <c r="I1260" s="1"/>
-    </row>
-    <row r="1261" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1261" s="1"/>
-    </row>
-    <row r="1262" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1262" s="2"/>
-      <c r="I1262" s="1"/>
-    </row>
-    <row r="1263" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1263" s="2"/>
-      <c r="I1263" s="1"/>
-    </row>
-    <row r="1264" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1264" s="2"/>
-      <c r="I1264" s="1"/>
-    </row>
-    <row r="1265" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1265" s="2"/>
-      <c r="I1265" s="1"/>
-    </row>
-    <row r="1266" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1266" s="2"/>
-      <c r="I1266" s="1"/>
-    </row>
-    <row r="1267" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1267" s="2"/>
-      <c r="I1267" s="1"/>
-    </row>
-    <row r="1268" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1268" s="2"/>
-      <c r="I1268" s="1"/>
-    </row>
-    <row r="1269" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1269" s="2"/>
-      <c r="I1269" s="1"/>
-    </row>
-    <row r="1270" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1270" s="2"/>
-      <c r="I1270" s="1"/>
-    </row>
-    <row r="1271" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1271" s="2"/>
-      <c r="I1271" s="1"/>
-    </row>
-    <row r="1272" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1272" s="2"/>
-      <c r="I1272" s="1"/>
-    </row>
-    <row r="1273" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1273" s="2"/>
-      <c r="I1273" s="1"/>
-    </row>
-    <row r="1274" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1274" s="1"/>
-    </row>
-    <row r="1275" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1275" s="2"/>
-      <c r="I1275" s="1"/>
-    </row>
-    <row r="1276" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1276" s="2"/>
-      <c r="I1276" s="1"/>
-    </row>
-    <row r="1277" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1277" s="2"/>
-      <c r="I1277" s="1"/>
-    </row>
-    <row r="1278" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1278" s="2"/>
-      <c r="I1278" s="1"/>
-    </row>
-    <row r="1279" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1256" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1257" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1257" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1257">
+        <v>1241</v>
+      </c>
+      <c r="D1257" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1257" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1257" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1257" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1257" s="1">
+        <v>46118.847916666666</v>
+      </c>
+      <c r="J1257">
+        <v>1</v>
+      </c>
+      <c r="K1257" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1258" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1258" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1258">
+        <v>1252</v>
+      </c>
+      <c r="D1258" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1258" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1258" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1258">
+        <v>0</v>
+      </c>
+      <c r="I1258" s="1">
+        <v>46118.848611111112</v>
+      </c>
+      <c r="J1258">
+        <v>1</v>
+      </c>
+      <c r="K1258" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1259" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1259" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1259">
+        <v>1748</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1259" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1259" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1259" s="2">
+        <v>6.5624999999999998E-3</v>
+      </c>
+      <c r="I1259" s="1">
+        <v>46118.849305555559</v>
+      </c>
+      <c r="J1259">
+        <v>0</v>
+      </c>
+      <c r="K1259" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1260" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1260" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1260">
+        <v>1749</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1260" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1260" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1260" s="2">
+        <v>6.898148148148148E-3</v>
+      </c>
+      <c r="I1260" s="1">
+        <v>46118.85</v>
+      </c>
+      <c r="J1260">
+        <v>1</v>
+      </c>
+      <c r="K1260" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1261" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1261" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1261">
+        <v>1754</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1261" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1261" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1261" s="2">
+        <v>6.5277777777777782E-3</v>
+      </c>
+      <c r="I1261" s="1">
+        <v>46118.85</v>
+      </c>
+      <c r="J1261">
+        <v>0</v>
+      </c>
+      <c r="K1261" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1262" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1262" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1262">
+        <v>3168</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1262" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1262" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1262" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1262" s="1">
+        <v>46118.850694444445</v>
+      </c>
+      <c r="J1262">
+        <v>1</v>
+      </c>
+      <c r="K1262" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1263" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1263" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1263">
+        <v>1249</v>
+      </c>
+      <c r="D1263" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1263" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1263" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1263" s="2">
+        <v>1.0810185185185185E-2</v>
+      </c>
+      <c r="I1263" s="1">
+        <v>46118.850694444445</v>
+      </c>
+      <c r="J1263">
+        <v>1</v>
+      </c>
+      <c r="K1263" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1264" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1264" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1264">
+        <v>1265</v>
+      </c>
+      <c r="D1264" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1264" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1264" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1264" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1264" s="1">
+        <v>46118.851388888892</v>
+      </c>
+      <c r="J1264">
+        <v>1</v>
+      </c>
+      <c r="K1264" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1265" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1265" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1265">
+        <v>5046</v>
+      </c>
+      <c r="D1265" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1265" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1265" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1265" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1265" s="1">
+        <v>46118.852083333331</v>
+      </c>
+      <c r="J1265">
+        <v>1</v>
+      </c>
+      <c r="K1265" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1266" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1266" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1266">
+        <v>5209</v>
+      </c>
+      <c r="D1266" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1266" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1266" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1266" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1266" s="1">
+        <v>46118.852083333331</v>
+      </c>
+      <c r="J1266">
+        <v>1</v>
+      </c>
+      <c r="K1266" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1267" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1267" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1267">
+        <v>3195</v>
+      </c>
+      <c r="D1267" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1267" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1267" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1267" s="2">
+        <v>7.1412037037037034E-3</v>
+      </c>
+      <c r="I1267" s="1">
+        <v>46118.852777777778</v>
+      </c>
+      <c r="J1267">
+        <v>0</v>
+      </c>
+      <c r="K1267" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1268" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1268" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1268">
+        <v>1263</v>
+      </c>
+      <c r="D1268" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1268" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1268" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1268" s="2">
+        <v>8.0439814814814818E-3</v>
+      </c>
+      <c r="I1268" s="1">
+        <v>46118.852777777778</v>
+      </c>
+      <c r="J1268">
+        <v>1</v>
+      </c>
+      <c r="K1268" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1269" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1269" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1269">
+        <v>1245</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1269" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1269" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1269" s="2">
+        <v>1.369212962962963E-2</v>
+      </c>
+      <c r="I1269" s="1">
+        <v>46118.853472222225</v>
+      </c>
+      <c r="J1269">
+        <v>1</v>
+      </c>
+      <c r="K1269" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1270" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1270" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1270">
+        <v>1248</v>
+      </c>
+      <c r="D1270" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1270" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1270" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1270" s="2">
+        <v>6.9907407407407409E-3</v>
+      </c>
+      <c r="I1270" s="1">
+        <v>46118.853472222225</v>
+      </c>
+      <c r="J1270">
+        <v>1</v>
+      </c>
+      <c r="K1270" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1271" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1271" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1271">
+        <v>1275</v>
+      </c>
+      <c r="D1271" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1271" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1271" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1271" s="2">
+        <v>7.5925925925925926E-3</v>
+      </c>
+      <c r="I1271" s="1">
+        <v>46118.854166666664</v>
+      </c>
+      <c r="J1271">
+        <v>1</v>
+      </c>
+      <c r="K1271" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1272" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1272" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1272">
+        <v>1761</v>
+      </c>
+      <c r="D1272" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1272" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1272" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1272" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1272" s="1">
+        <v>46118.854166666664</v>
+      </c>
+      <c r="J1272">
+        <v>1</v>
+      </c>
+      <c r="K1272" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1273" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1273" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1273">
+        <v>2001</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1273" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1273" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1273" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1273" s="1">
+        <v>46118.854861111111</v>
+      </c>
+      <c r="J1273">
+        <v>1</v>
+      </c>
+      <c r="K1273" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1274" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1274" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1274">
+        <v>2000</v>
+      </c>
+      <c r="D1274" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1274" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1274" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1274" s="2">
+        <v>8.1712962962962963E-3</v>
+      </c>
+      <c r="I1274" s="1">
+        <v>46118.855555555558</v>
+      </c>
+      <c r="J1274">
+        <v>0</v>
+      </c>
+      <c r="K1274" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1275" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1275" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1275">
+        <v>1258</v>
+      </c>
+      <c r="D1275" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1275" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1275" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1275" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1275" s="1">
+        <v>46118.855555555558</v>
+      </c>
+      <c r="J1275">
+        <v>1</v>
+      </c>
+      <c r="K1275" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1276" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1276" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1276">
+        <v>1266</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1276" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1276" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1276" s="2">
+        <v>1.6701388888888891E-2</v>
+      </c>
+      <c r="I1276" s="1">
+        <v>46118.834837962961</v>
+      </c>
+      <c r="J1276">
+        <v>1</v>
+      </c>
+      <c r="K1276" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1277" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1277" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1277">
+        <v>1755</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1277" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1277" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1277" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1277" s="1">
+        <v>46118.835532407407</v>
+      </c>
+      <c r="J1277">
+        <v>1</v>
+      </c>
+      <c r="K1277" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1278" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1278" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1278">
+        <v>1267</v>
+      </c>
+      <c r="D1278" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1278" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1278" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1278" s="2">
+        <v>8.9467592592592585E-3</v>
+      </c>
+      <c r="I1278" s="1">
+        <v>46118.835532407407</v>
+      </c>
+      <c r="J1278">
+        <v>0</v>
+      </c>
+      <c r="K1278" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1279" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
     </row>
-    <row r="1280" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1280" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1280" s="2"/>
       <c r="I1280" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Voyager - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073291F5-8A1F-485E-B63A-294614481CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BE6F07-CA6B-4791-A886-E0A33099D79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6078" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6083" uniqueCount="128">
   <si>
     <t>Company Name</t>
   </si>
@@ -420,6 +420,9 @@
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
+  </si>
+  <si>
+    <t>4 Clocks HOS-Basics</t>
   </si>
 </sst>
 </file>
@@ -35485,7 +35488,7 @@
         <v>46118.847916666666</v>
       </c>
       <c r="J1257">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1257" t="s">
         <v>11</v>
@@ -35514,7 +35517,7 @@
         <v>46118.848611111112</v>
       </c>
       <c r="J1258">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1258" t="s">
         <v>11</v>
@@ -35630,7 +35633,7 @@
         <v>46118.850694444445</v>
       </c>
       <c r="J1262">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1262" t="s">
         <v>11</v>
@@ -35679,16 +35682,16 @@
         <v>126</v>
       </c>
       <c r="G1264" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1264" s="2">
-        <v>0</v>
+        <v>9.3749999999999997E-3</v>
       </c>
       <c r="I1264" s="1">
         <v>46118.851388888892</v>
       </c>
       <c r="J1264">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1264" t="s">
         <v>11</v>
@@ -35717,7 +35720,7 @@
         <v>46118.852083333331</v>
       </c>
       <c r="J1265">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1265" t="s">
         <v>11</v>
@@ -35746,7 +35749,7 @@
         <v>46118.852083333331</v>
       </c>
       <c r="J1266">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1266" t="s">
         <v>11</v>
@@ -35911,16 +35914,16 @@
         <v>126</v>
       </c>
       <c r="G1272" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1272" s="2">
-        <v>0</v>
+        <v>7.9629629629629634E-3</v>
       </c>
       <c r="I1272" s="1">
         <v>46118.854166666664</v>
       </c>
       <c r="J1272">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1272" t="s">
         <v>11</v>
@@ -35949,7 +35952,7 @@
         <v>46118.854861111111</v>
       </c>
       <c r="J1273">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1273" t="s">
         <v>11</v>
@@ -36007,7 +36010,7 @@
         <v>46118.855555555558</v>
       </c>
       <c r="J1275">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1275" t="s">
         <v>11</v>
@@ -36065,7 +36068,7 @@
         <v>46118.835532407407</v>
       </c>
       <c r="J1277">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1277" t="s">
         <v>11</v>
@@ -36101,8 +36104,33 @@
       </c>
     </row>
     <row r="1279" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1279" s="2"/>
-      <c r="I1279" s="1"/>
+      <c r="B1279" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1279">
+        <v>2001</v>
+      </c>
+      <c r="D1279" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1279" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1279" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1279" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1279" s="1">
+        <v>46128.793865740743</v>
+      </c>
+      <c r="J1279">
+        <v>0</v>
+      </c>
+      <c r="K1279" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1280" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1280" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Voyager - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BE6F07-CA6B-4791-A886-E0A33099D79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9960FCDA-FF23-4B89-94AF-E583B112C6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6083" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6084" uniqueCount="128">
   <si>
     <t>Company Name</t>
   </si>
@@ -35488,7 +35488,7 @@
         <v>46118.847916666666</v>
       </c>
       <c r="J1257">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1257" t="s">
         <v>11</v>
@@ -35517,7 +35517,7 @@
         <v>46118.848611111112</v>
       </c>
       <c r="J1258">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1258" t="s">
         <v>11</v>
@@ -35624,16 +35624,16 @@
         <v>126</v>
       </c>
       <c r="G1262" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1262" s="2">
-        <v>0</v>
+        <v>8.5879629629629622E-3</v>
       </c>
       <c r="I1262" s="1">
         <v>46118.850694444445</v>
       </c>
       <c r="J1262">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1262" t="s">
         <v>11</v>
@@ -35711,16 +35711,16 @@
         <v>126</v>
       </c>
       <c r="G1265" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1265" s="2">
-        <v>0</v>
+        <v>8.8425925925925929E-3</v>
       </c>
       <c r="I1265" s="1">
         <v>46118.852083333331</v>
       </c>
       <c r="J1265">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1265" t="s">
         <v>11</v>
@@ -35740,10 +35740,10 @@
         <v>126</v>
       </c>
       <c r="G1266" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H1266" s="2">
-        <v>0</v>
+        <v>2.3263888888888887E-3</v>
       </c>
       <c r="I1266" s="1">
         <v>46118.852083333331</v>
@@ -35756,32 +35756,10 @@
       </c>
     </row>
     <row r="1267" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1267" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1267">
-        <v>3195</v>
-      </c>
-      <c r="D1267" t="s">
-        <v>118</v>
-      </c>
-      <c r="F1267" t="s">
-        <v>126</v>
-      </c>
-      <c r="G1267" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1267" s="2">
-        <v>7.1412037037037034E-3</v>
-      </c>
-      <c r="I1267" s="1">
-        <v>46118.852777777778</v>
-      </c>
-      <c r="J1267">
-        <v>0</v>
-      </c>
+      <c r="H1267" s="2"/>
+      <c r="I1267" s="1"/>
       <c r="K1267" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1268" spans="2:11" x14ac:dyDescent="0.25">
@@ -35789,10 +35767,10 @@
         <v>41</v>
       </c>
       <c r="C1268">
-        <v>1263</v>
+        <v>3195</v>
       </c>
       <c r="D1268" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="F1268" t="s">
         <v>126</v>
@@ -35801,13 +35779,13 @@
         <v>10</v>
       </c>
       <c r="H1268" s="2">
-        <v>8.0439814814814818E-3</v>
+        <v>7.1412037037037034E-3</v>
       </c>
       <c r="I1268" s="1">
         <v>46118.852777777778</v>
       </c>
       <c r="J1268">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1268" t="s">
         <v>11</v>
@@ -35818,10 +35796,10 @@
         <v>41</v>
       </c>
       <c r="C1269">
-        <v>1245</v>
+        <v>1263</v>
       </c>
       <c r="D1269" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F1269" t="s">
         <v>126</v>
@@ -35830,10 +35808,10 @@
         <v>10</v>
       </c>
       <c r="H1269" s="2">
-        <v>1.369212962962963E-2</v>
+        <v>8.0439814814814818E-3</v>
       </c>
       <c r="I1269" s="1">
-        <v>46118.853472222225</v>
+        <v>46118.852777777778</v>
       </c>
       <c r="J1269">
         <v>1</v>
@@ -35847,10 +35825,10 @@
         <v>41</v>
       </c>
       <c r="C1270">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="D1270" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F1270" t="s">
         <v>126</v>
@@ -35859,7 +35837,7 @@
         <v>10</v>
       </c>
       <c r="H1270" s="2">
-        <v>6.9907407407407409E-3</v>
+        <v>1.369212962962963E-2</v>
       </c>
       <c r="I1270" s="1">
         <v>46118.853472222225</v>
@@ -35876,10 +35854,10 @@
         <v>41</v>
       </c>
       <c r="C1271">
-        <v>1275</v>
+        <v>1248</v>
       </c>
       <c r="D1271" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F1271" t="s">
         <v>126</v>
@@ -35888,10 +35866,10 @@
         <v>10</v>
       </c>
       <c r="H1271" s="2">
-        <v>7.5925925925925926E-3</v>
+        <v>6.9907407407407409E-3</v>
       </c>
       <c r="I1271" s="1">
-        <v>46118.854166666664</v>
+        <v>46118.853472222225</v>
       </c>
       <c r="J1271">
         <v>1</v>
@@ -35905,10 +35883,10 @@
         <v>41</v>
       </c>
       <c r="C1272">
-        <v>1761</v>
+        <v>1275</v>
       </c>
       <c r="D1272" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F1272" t="s">
         <v>126</v>
@@ -35917,13 +35895,13 @@
         <v>10</v>
       </c>
       <c r="H1272" s="2">
-        <v>7.9629629629629634E-3</v>
+        <v>7.5925925925925926E-3</v>
       </c>
       <c r="I1272" s="1">
         <v>46118.854166666664</v>
       </c>
       <c r="J1272">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1272" t="s">
         <v>11</v>
@@ -35934,22 +35912,22 @@
         <v>41</v>
       </c>
       <c r="C1273">
-        <v>2001</v>
+        <v>1761</v>
       </c>
       <c r="D1273" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="F1273" t="s">
         <v>126</v>
       </c>
       <c r="G1273" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1273" s="2">
-        <v>0</v>
+        <v>7.9629629629629634E-3</v>
       </c>
       <c r="I1273" s="1">
-        <v>46118.854861111111</v>
+        <v>46118.854166666664</v>
       </c>
       <c r="J1273">
         <v>2</v>
@@ -35963,25 +35941,25 @@
         <v>41</v>
       </c>
       <c r="C1274">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="D1274" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F1274" t="s">
         <v>126</v>
       </c>
       <c r="G1274" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1274" s="2">
-        <v>8.1712962962962963E-3</v>
+        <v>0</v>
       </c>
       <c r="I1274" s="1">
-        <v>46118.855555555558</v>
+        <v>46118.854861111111</v>
       </c>
       <c r="J1274">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1274" t="s">
         <v>11</v>
@@ -35992,25 +35970,25 @@
         <v>41</v>
       </c>
       <c r="C1275">
-        <v>1258</v>
+        <v>2000</v>
       </c>
       <c r="D1275" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F1275" t="s">
         <v>126</v>
       </c>
       <c r="G1275" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1275" s="2">
-        <v>0</v>
+        <v>8.1712962962962963E-3</v>
       </c>
       <c r="I1275" s="1">
         <v>46118.855555555558</v>
       </c>
       <c r="J1275">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1275" t="s">
         <v>11</v>
@@ -36021,10 +35999,10 @@
         <v>41</v>
       </c>
       <c r="C1276">
-        <v>1266</v>
+        <v>1258</v>
       </c>
       <c r="D1276" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F1276" t="s">
         <v>126</v>
@@ -36033,13 +36011,13 @@
         <v>10</v>
       </c>
       <c r="H1276" s="2">
-        <v>1.6701388888888891E-2</v>
+        <v>6.0069444444444441E-3</v>
       </c>
       <c r="I1276" s="1">
-        <v>46118.834837962961</v>
+        <v>46118.855555555558</v>
       </c>
       <c r="J1276">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1276" t="s">
         <v>11</v>
@@ -36050,25 +36028,25 @@
         <v>41</v>
       </c>
       <c r="C1277">
-        <v>1755</v>
+        <v>1266</v>
       </c>
       <c r="D1277" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F1277" t="s">
         <v>126</v>
       </c>
       <c r="G1277" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1277" s="2">
-        <v>0</v>
+        <v>1.6701388888888891E-2</v>
       </c>
       <c r="I1277" s="1">
-        <v>46118.835532407407</v>
+        <v>46118.834837962961</v>
       </c>
       <c r="J1277">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1277" t="s">
         <v>11</v>
@@ -36079,25 +36057,25 @@
         <v>41</v>
       </c>
       <c r="C1278">
-        <v>1267</v>
+        <v>1755</v>
       </c>
       <c r="D1278" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F1278" t="s">
         <v>126</v>
       </c>
       <c r="G1278" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1278" s="2">
-        <v>8.9467592592592585E-3</v>
+        <v>0</v>
       </c>
       <c r="I1278" s="1">
         <v>46118.835532407407</v>
       </c>
       <c r="J1278">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1278" t="s">
         <v>11</v>
@@ -36108,33 +36086,58 @@
         <v>41</v>
       </c>
       <c r="C1279">
+        <v>1267</v>
+      </c>
+      <c r="D1279" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1279" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1279" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1279" s="2">
+        <v>8.9467592592592585E-3</v>
+      </c>
+      <c r="I1279" s="1">
+        <v>46118.835532407407</v>
+      </c>
+      <c r="J1279">
+        <v>0</v>
+      </c>
+      <c r="K1279" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1280" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1280" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1280">
         <v>2001</v>
       </c>
-      <c r="D1279" t="s">
+      <c r="D1280" t="s">
         <v>108</v>
       </c>
-      <c r="F1279" t="s">
+      <c r="F1280" t="s">
         <v>127</v>
       </c>
-      <c r="G1279" t="s">
+      <c r="G1280" t="s">
         <v>13</v>
       </c>
-      <c r="H1279" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1279" s="1">
+      <c r="H1280" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1280" s="1">
         <v>46128.793865740743</v>
       </c>
-      <c r="J1279">
-        <v>0</v>
-      </c>
-      <c r="K1279" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1280" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1280" s="2"/>
-      <c r="I1280" s="1"/>
+      <c r="J1280">
+        <v>1</v>
+      </c>
+      <c r="K1280" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1281" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H1281" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Voyager - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9960FCDA-FF23-4B89-94AF-E583B112C6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8554EAFB-B775-4FE8-86EA-6FCC8950A4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6084" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6269" uniqueCount="130">
   <si>
     <t>Company Name</t>
   </si>
@@ -423,6 +423,12 @@
   </si>
   <si>
     <t>4 Clocks HOS-Basics</t>
+  </si>
+  <si>
+    <t>Rules for Safe Driving</t>
+  </si>
+  <si>
+    <t>KELLY GNIETING</t>
   </si>
 </sst>
 </file>
@@ -35479,16 +35485,16 @@
         <v>126</v>
       </c>
       <c r="G1257" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1257" s="2">
-        <v>0</v>
+        <v>8.3217592592592596E-3</v>
       </c>
       <c r="I1257" s="1">
         <v>46118.847916666666</v>
       </c>
       <c r="J1257">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1257" t="s">
         <v>11</v>
@@ -35508,16 +35514,16 @@
         <v>126</v>
       </c>
       <c r="G1258" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1258">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H1258" s="2">
+        <v>6.6087962962962966E-3</v>
       </c>
       <c r="I1258" s="1">
         <v>46118.848611111112</v>
       </c>
       <c r="J1258">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1258" t="s">
         <v>11</v>
@@ -35959,7 +35965,7 @@
         <v>46118.854861111111</v>
       </c>
       <c r="J1274">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1274" t="s">
         <v>11</v>
@@ -36066,10 +36072,10 @@
         <v>126</v>
       </c>
       <c r="G1278" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1278" s="2">
-        <v>0</v>
+        <v>7.8935185185185185E-3</v>
       </c>
       <c r="I1278" s="1">
         <v>46118.835532407407</v>
@@ -36133,199 +36139,1125 @@
         <v>46128.793865740743</v>
       </c>
       <c r="J1280">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1280" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="1281" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1281" s="2"/>
-      <c r="I1281" s="1"/>
-    </row>
-    <row r="1282" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1282" s="2"/>
-      <c r="I1282" s="1"/>
-    </row>
-    <row r="1283" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1283" s="2"/>
-      <c r="I1283" s="1"/>
-    </row>
-    <row r="1284" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1284" s="2"/>
-      <c r="I1284" s="1"/>
-    </row>
-    <row r="1285" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1285" s="2"/>
-      <c r="I1285" s="1"/>
-    </row>
-    <row r="1286" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1286" s="2"/>
-      <c r="I1286" s="1"/>
-    </row>
-    <row r="1287" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1287" s="2"/>
-      <c r="I1287" s="1"/>
-    </row>
-    <row r="1288" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1288" s="2"/>
-      <c r="I1288" s="1"/>
-    </row>
-    <row r="1289" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1289" s="2"/>
-      <c r="I1289" s="1"/>
-    </row>
-    <row r="1290" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1290" s="2"/>
-      <c r="I1290" s="1"/>
-    </row>
-    <row r="1291" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1291" s="2"/>
-      <c r="I1291" s="1"/>
-    </row>
-    <row r="1292" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1292" s="2"/>
-      <c r="I1292" s="1"/>
-    </row>
-    <row r="1293" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1293" s="2"/>
-      <c r="I1293" s="1"/>
-    </row>
-    <row r="1294" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1294" s="2"/>
-      <c r="I1294" s="1"/>
-    </row>
-    <row r="1295" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1295" s="2"/>
-      <c r="I1295" s="1"/>
-    </row>
-    <row r="1296" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1296" s="2"/>
-      <c r="I1296" s="1"/>
-    </row>
-    <row r="1297" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1297" s="2"/>
-      <c r="I1297" s="1"/>
-    </row>
-    <row r="1298" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1298" s="2"/>
-      <c r="I1298" s="1"/>
-    </row>
-    <row r="1299" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1299" s="2"/>
-      <c r="I1299" s="1"/>
-    </row>
-    <row r="1300" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1300" s="1"/>
-    </row>
-    <row r="1301" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1301" s="2"/>
-      <c r="I1301" s="1"/>
-    </row>
-    <row r="1302" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1302" s="2"/>
-      <c r="I1302" s="1"/>
-    </row>
-    <row r="1303" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1303" s="2"/>
-      <c r="I1303" s="1"/>
-    </row>
-    <row r="1304" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1304" s="2"/>
-      <c r="I1304" s="1"/>
-    </row>
-    <row r="1305" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1305" s="2"/>
-      <c r="I1305" s="1"/>
-    </row>
-    <row r="1306" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1306" s="2"/>
-      <c r="I1306" s="1"/>
-    </row>
-    <row r="1307" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1307" s="2"/>
-      <c r="I1307" s="1"/>
-    </row>
-    <row r="1308" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1308" s="2"/>
-      <c r="I1308" s="1"/>
-    </row>
-    <row r="1309" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1309" s="2"/>
-      <c r="I1309" s="1"/>
-    </row>
-    <row r="1310" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1310" s="2"/>
-      <c r="I1310" s="1"/>
-    </row>
-    <row r="1311" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1311" s="2"/>
-      <c r="I1311" s="1"/>
-    </row>
-    <row r="1312" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1312" s="2"/>
-      <c r="I1312" s="1"/>
-    </row>
-    <row r="1313" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1313" s="2"/>
-      <c r="I1313" s="1"/>
-    </row>
-    <row r="1314" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1314" s="2"/>
-      <c r="I1314" s="1"/>
-    </row>
-    <row r="1315" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1315" s="2"/>
-      <c r="I1315" s="1"/>
-    </row>
-    <row r="1316" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1316" s="2"/>
-      <c r="I1316" s="1"/>
-    </row>
-    <row r="1317" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1317" s="2"/>
-      <c r="I1317" s="1"/>
-    </row>
-    <row r="1318" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1281" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1281" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1281">
+        <v>3326</v>
+      </c>
+      <c r="D1281" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1281" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1281" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1281" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1281" s="1">
+        <v>46146.717824074076</v>
+      </c>
+      <c r="J1281">
+        <v>0</v>
+      </c>
+      <c r="K1281" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1282" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1282" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1282">
+        <v>1256</v>
+      </c>
+      <c r="D1282" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1282" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1282" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1282" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1282" s="1">
+        <v>46146.718518518515</v>
+      </c>
+      <c r="J1282">
+        <v>0</v>
+      </c>
+      <c r="K1282" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1283" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1283" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1283">
+        <v>3528</v>
+      </c>
+      <c r="D1283" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1283" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1283" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1283" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1283" s="1">
+        <v>46146.719212962962</v>
+      </c>
+      <c r="J1283">
+        <v>0</v>
+      </c>
+      <c r="K1283" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1284" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1284" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1284">
+        <v>1751</v>
+      </c>
+      <c r="D1284" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1284" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1284" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1284" s="2">
+        <v>4.8263888888888887E-3</v>
+      </c>
+      <c r="I1284" s="1">
+        <v>46146.719212962962</v>
+      </c>
+      <c r="J1284">
+        <v>0</v>
+      </c>
+      <c r="K1284" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1285" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1285" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1285">
+        <v>1278</v>
+      </c>
+      <c r="D1285" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1285" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1285" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1285" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1285" s="1">
+        <v>46146.719907407409</v>
+      </c>
+      <c r="J1285">
+        <v>0</v>
+      </c>
+      <c r="K1285" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1286" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1286" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1286">
+        <v>1262</v>
+      </c>
+      <c r="D1286" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1286" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1286" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1286" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1286" s="1">
+        <v>46146.720601851855</v>
+      </c>
+      <c r="J1286">
+        <v>0</v>
+      </c>
+      <c r="K1286" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1287" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1287" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1287">
+        <v>1276</v>
+      </c>
+      <c r="D1287" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1287" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1287" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1287" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1287" s="1">
+        <v>46146.720601851855</v>
+      </c>
+      <c r="J1287">
+        <v>0</v>
+      </c>
+      <c r="K1287" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1288" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1288" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1288">
+        <v>2917</v>
+      </c>
+      <c r="D1288" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1288" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1288" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1288" s="2">
+        <v>4.178240740740741E-3</v>
+      </c>
+      <c r="I1288" s="1">
+        <v>46146.721296296295</v>
+      </c>
+      <c r="J1288">
+        <v>0</v>
+      </c>
+      <c r="K1288" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1289" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1289" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1289">
+        <v>1250</v>
+      </c>
+      <c r="D1289" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1289" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1289" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1289" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1289" s="1">
+        <v>46146.721990740742</v>
+      </c>
+      <c r="J1289">
+        <v>0</v>
+      </c>
+      <c r="K1289" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1290" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1290" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1290">
+        <v>3294</v>
+      </c>
+      <c r="D1290" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1290" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1290" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1290" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1290" s="1">
+        <v>46146.721990740742</v>
+      </c>
+      <c r="J1290">
+        <v>0</v>
+      </c>
+      <c r="K1290" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1291" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1291" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1291">
+        <v>1762</v>
+      </c>
+      <c r="D1291" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1291" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1291" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1291" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1291" s="1">
+        <v>46146.722685185188</v>
+      </c>
+      <c r="J1291">
+        <v>0</v>
+      </c>
+      <c r="K1291" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1292" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1292" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1292">
+        <v>2936</v>
+      </c>
+      <c r="D1292" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1292" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1292" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1292" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1292" s="1">
+        <v>46146.723379629628</v>
+      </c>
+      <c r="J1292">
+        <v>0</v>
+      </c>
+      <c r="K1292" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1293" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1293" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1293">
+        <v>1272</v>
+      </c>
+      <c r="D1293" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1293" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1293" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1293" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1293" s="1">
+        <v>46146.723379629628</v>
+      </c>
+      <c r="J1293">
+        <v>0</v>
+      </c>
+      <c r="K1293" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1294" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1294" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1294">
+        <v>1257</v>
+      </c>
+      <c r="D1294" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1294" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1294" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1294" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1294" s="1">
+        <v>46146.724074074074</v>
+      </c>
+      <c r="J1294">
+        <v>0</v>
+      </c>
+      <c r="K1294" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1295" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1295" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1295">
+        <v>1241</v>
+      </c>
+      <c r="D1295" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1295" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1295" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1295" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1295" s="1">
+        <v>46146.724768518521</v>
+      </c>
+      <c r="J1295">
+        <v>0</v>
+      </c>
+      <c r="K1295" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1296" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1296" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1296">
+        <v>1252</v>
+      </c>
+      <c r="D1296" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1296" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1296" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1296" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1296" s="1">
+        <v>46146.724768518521</v>
+      </c>
+      <c r="J1296">
+        <v>0</v>
+      </c>
+      <c r="K1296" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1297" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1297" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1297">
+        <v>1748</v>
+      </c>
+      <c r="D1297" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1297" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1297" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1297" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1297" s="1">
+        <v>46146.725462962961</v>
+      </c>
+      <c r="J1297">
+        <v>0</v>
+      </c>
+      <c r="K1297" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1298" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1298" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1298">
+        <v>1749</v>
+      </c>
+      <c r="D1298" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1298" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1298" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1298" s="2">
+        <v>4.2824074074074075E-3</v>
+      </c>
+      <c r="I1298" s="1">
+        <v>46146.726157407407</v>
+      </c>
+      <c r="J1298">
+        <v>0</v>
+      </c>
+      <c r="K1298" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1299" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1299" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1299">
+        <v>5526</v>
+      </c>
+      <c r="D1299" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1299" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1299" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1299" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1299" s="1">
+        <v>46146.726157407407</v>
+      </c>
+      <c r="J1299">
+        <v>0</v>
+      </c>
+      <c r="K1299" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1300" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1300" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1300">
+        <v>1754</v>
+      </c>
+      <c r="D1300" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1300" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1300" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1300" s="2">
+        <v>4.6412037037037038E-3</v>
+      </c>
+      <c r="I1300" s="1">
+        <v>46146.726851851854</v>
+      </c>
+      <c r="J1300">
+        <v>0</v>
+      </c>
+      <c r="K1300" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1301" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1301" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1301">
+        <v>3168</v>
+      </c>
+      <c r="D1301" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1301" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1301" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1301" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1301" s="1">
+        <v>46146.727546296293</v>
+      </c>
+      <c r="J1301">
+        <v>0</v>
+      </c>
+      <c r="K1301" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1302" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1302" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1302">
+        <v>1249</v>
+      </c>
+      <c r="D1302" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1302" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1302" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1302" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1302" s="1">
+        <v>46146.727546296293</v>
+      </c>
+      <c r="J1302">
+        <v>0</v>
+      </c>
+      <c r="K1302" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1303" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1303" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1303">
+        <v>1265</v>
+      </c>
+      <c r="D1303" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1303" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1303" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1303" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1303" s="1">
+        <v>46146.72824074074</v>
+      </c>
+      <c r="J1303">
+        <v>0</v>
+      </c>
+      <c r="K1303" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1304" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1304" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1304">
+        <v>5046</v>
+      </c>
+      <c r="D1304" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1304" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1304" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1304" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1304" s="1">
+        <v>46146.728935185187</v>
+      </c>
+      <c r="J1304">
+        <v>0</v>
+      </c>
+      <c r="K1304" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1305" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1305" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1305">
+        <v>5209</v>
+      </c>
+      <c r="D1305" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1305" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1305" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1305" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1305" s="1">
+        <v>46146.728935185187</v>
+      </c>
+      <c r="J1305">
+        <v>0</v>
+      </c>
+      <c r="K1305" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1306" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1306" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1306">
+        <v>3195</v>
+      </c>
+      <c r="D1306" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1306" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1306" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1306" s="2">
+        <v>4.0972222222222226E-3</v>
+      </c>
+      <c r="I1306" s="1">
+        <v>46146.729629629626</v>
+      </c>
+      <c r="J1306">
+        <v>0</v>
+      </c>
+      <c r="K1306" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1307" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1307" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1307">
+        <v>1263</v>
+      </c>
+      <c r="D1307" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1307" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1307" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1307" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1307" s="1">
+        <v>46146.730324074073</v>
+      </c>
+      <c r="J1307">
+        <v>0</v>
+      </c>
+      <c r="K1307" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1308" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1308" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1308">
+        <v>1245</v>
+      </c>
+      <c r="D1308" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1308" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1308" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1308" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1308" s="1">
+        <v>46146.730324074073</v>
+      </c>
+      <c r="J1308">
+        <v>0</v>
+      </c>
+      <c r="K1308" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1309" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1309" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1309">
+        <v>1248</v>
+      </c>
+      <c r="D1309" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1309" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1309" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1309" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1309" s="1">
+        <v>46146.73101851852</v>
+      </c>
+      <c r="J1309">
+        <v>0</v>
+      </c>
+      <c r="K1309" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1310" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1310" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1310">
+        <v>1275</v>
+      </c>
+      <c r="D1310" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1310" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1310" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1310" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1310" s="1">
+        <v>46146.731712962966</v>
+      </c>
+      <c r="J1310">
+        <v>0</v>
+      </c>
+      <c r="K1310" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1311" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1311" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1311">
+        <v>1761</v>
+      </c>
+      <c r="D1311" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1311" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1311" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1311" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1311" s="1">
+        <v>46146.731712962966</v>
+      </c>
+      <c r="J1311">
+        <v>0</v>
+      </c>
+      <c r="K1311" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1312" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1312" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1312">
+        <v>2001</v>
+      </c>
+      <c r="D1312" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1312" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1312" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1312" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1312" s="1">
+        <v>46146.732407407406</v>
+      </c>
+      <c r="J1312">
+        <v>0</v>
+      </c>
+      <c r="K1312" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1313" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1313" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1313">
+        <v>2000</v>
+      </c>
+      <c r="D1313" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1313" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1313" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1313" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1313" s="1">
+        <v>46146.733101851853</v>
+      </c>
+      <c r="J1313">
+        <v>0</v>
+      </c>
+      <c r="K1313" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1314" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1314" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1314">
+        <v>1258</v>
+      </c>
+      <c r="D1314" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1314" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1314" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1314" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1314" s="1">
+        <v>46146.710300925923</v>
+      </c>
+      <c r="J1314">
+        <v>0</v>
+      </c>
+      <c r="K1314" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1315" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1315" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1315">
+        <v>1266</v>
+      </c>
+      <c r="D1315" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1315" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1315" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1315" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1315" s="1">
+        <v>46146.710995370369</v>
+      </c>
+      <c r="J1315">
+        <v>0</v>
+      </c>
+      <c r="K1315" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1316" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1316" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1316">
+        <v>1755</v>
+      </c>
+      <c r="D1316" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1316" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1316" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1316" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1316" s="1">
+        <v>46146.710995370369</v>
+      </c>
+      <c r="J1316">
+        <v>0</v>
+      </c>
+      <c r="K1316" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1317" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1317" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1317">
+        <v>1267</v>
+      </c>
+      <c r="D1317" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1317" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1317" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1317" s="2">
+        <v>6.828703703703704E-3</v>
+      </c>
+      <c r="I1317" s="1">
+        <v>46146.711689814816</v>
+      </c>
+      <c r="J1317">
+        <v>0</v>
+      </c>
+      <c r="K1317" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1318" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1318" s="2"/>
       <c r="I1318" s="1"/>
     </row>
-    <row r="1319" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1319" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1319" s="2"/>
       <c r="I1319" s="1"/>
     </row>
-    <row r="1320" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1320" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1320" s="2"/>
       <c r="I1320" s="1"/>
     </row>
-    <row r="1321" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1321" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1321" s="2"/>
       <c r="I1321" s="1"/>
     </row>
-    <row r="1322" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1322" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1322" s="2"/>
       <c r="I1322" s="1"/>
     </row>
-    <row r="1323" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1323" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1323" s="2"/>
       <c r="I1323" s="1"/>
     </row>
-    <row r="1324" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1324" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1324" s="2"/>
       <c r="I1324" s="1"/>
     </row>
-    <row r="1325" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1325" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1325" s="1"/>
     </row>
-    <row r="1326" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1326" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1326" s="2"/>
       <c r="I1326" s="1"/>
     </row>
-    <row r="1327" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1327" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1327" s="2"/>
       <c r="I1327" s="1"/>
     </row>
-    <row r="1328" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1328" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1328" s="2"/>
       <c r="I1328" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Voyager - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8554EAFB-B775-4FE8-86EA-6FCC8950A4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563C79DB-1631-4DA6-82BE-D87C12904D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -35956,16 +35956,16 @@
         <v>126</v>
       </c>
       <c r="G1274" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1274" s="2">
-        <v>0</v>
+        <v>7.3958333333333333E-3</v>
       </c>
       <c r="I1274" s="1">
         <v>46118.854861111111</v>
       </c>
       <c r="J1274">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1274" t="s">
         <v>11</v>
@@ -36130,16 +36130,16 @@
         <v>127</v>
       </c>
       <c r="G1280" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1280" s="2">
-        <v>0</v>
+        <v>7.9629629629629634E-3</v>
       </c>
       <c r="I1280" s="1">
         <v>46128.793865740743</v>
       </c>
       <c r="J1280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1280" t="s">
         <v>11</v>
@@ -36159,10 +36159,10 @@
         <v>128</v>
       </c>
       <c r="G1281" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1281" s="2">
-        <v>0</v>
+        <v>2.2453703703703702E-3</v>
       </c>
       <c r="I1281" s="1">
         <v>46146.717824074076</v>
@@ -36275,10 +36275,10 @@
         <v>128</v>
       </c>
       <c r="G1285" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1285" s="2">
-        <v>0</v>
+        <v>5.8101851851851856E-3</v>
       </c>
       <c r="I1285" s="1">
         <v>46146.719907407409</v>
@@ -36333,10 +36333,10 @@
         <v>128</v>
       </c>
       <c r="G1287" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1287" s="2">
-        <v>0</v>
+        <v>4.9652777777777777E-3</v>
       </c>
       <c r="I1287" s="1">
         <v>46146.720601851855</v>
@@ -36391,10 +36391,10 @@
         <v>128</v>
       </c>
       <c r="G1289" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1289" s="2">
-        <v>0</v>
+        <v>5.8564814814814816E-3</v>
       </c>
       <c r="I1289" s="1">
         <v>46146.721990740742</v>
@@ -36420,10 +36420,10 @@
         <v>128</v>
       </c>
       <c r="G1290" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1290" s="2">
-        <v>0</v>
+        <v>5.162037037037037E-3</v>
       </c>
       <c r="I1290" s="1">
         <v>46146.721990740742</v>
@@ -36478,10 +36478,10 @@
         <v>128</v>
       </c>
       <c r="G1292" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1292" s="2">
-        <v>0</v>
+        <v>6.2962962962962964E-3</v>
       </c>
       <c r="I1292" s="1">
         <v>46146.723379629628</v>
@@ -36507,10 +36507,10 @@
         <v>128</v>
       </c>
       <c r="G1293" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1293" s="2">
-        <v>0</v>
+        <v>5.9027777777777776E-3</v>
       </c>
       <c r="I1293" s="1">
         <v>46146.723379629628</v>
@@ -36536,10 +36536,10 @@
         <v>128</v>
       </c>
       <c r="G1294" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1294" s="2">
-        <v>0</v>
+        <v>5.4861111111111109E-3</v>
       </c>
       <c r="I1294" s="1">
         <v>46146.724074074074</v>
@@ -36797,10 +36797,10 @@
         <v>128</v>
       </c>
       <c r="G1303" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1303" s="2">
-        <v>0</v>
+        <v>5.115740740740741E-3</v>
       </c>
       <c r="I1303" s="1">
         <v>46146.72824074074</v>
@@ -36855,10 +36855,10 @@
         <v>128</v>
       </c>
       <c r="G1305" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1305" s="2">
-        <v>0</v>
+        <v>5.7175925925925927E-3</v>
       </c>
       <c r="I1305" s="1">
         <v>46146.728935185187</v>
@@ -36913,10 +36913,10 @@
         <v>128</v>
       </c>
       <c r="G1307" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1307" s="2">
-        <v>0</v>
+        <v>4.9768518518518521E-3</v>
       </c>
       <c r="I1307" s="1">
         <v>46146.730324074073</v>
@@ -36942,10 +36942,10 @@
         <v>128</v>
       </c>
       <c r="G1308" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1308" s="2">
-        <v>0</v>
+        <v>8.2060185185185187E-3</v>
       </c>
       <c r="I1308" s="1">
         <v>46146.730324074073</v>
@@ -37000,10 +37000,10 @@
         <v>128</v>
       </c>
       <c r="G1310" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1310" s="2">
-        <v>0</v>
+        <v>5.7523148148148151E-3</v>
       </c>
       <c r="I1310" s="1">
         <v>46146.731712962966</v>
@@ -37145,10 +37145,10 @@
         <v>128</v>
       </c>
       <c r="G1315" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1315" s="2">
-        <v>0</v>
+        <v>9.479166666666667E-3</v>
       </c>
       <c r="I1315" s="1">
         <v>46146.710995370369</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Voyager - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F0A538-8B1F-4885-8C22-4E9FA1A19307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB77911-C016-4C71-A7F6-B2A4EA288037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6275" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6277" uniqueCount="131">
   <si>
     <t>Company Name</t>
   </si>
@@ -36229,7 +36229,7 @@
         <v>46146.719212962962</v>
       </c>
       <c r="J1283">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1283" t="s">
         <v>11</v>
@@ -36461,7 +36461,7 @@
         <v>46146.722685185188</v>
       </c>
       <c r="J1291">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1291" t="s">
         <v>11</v>
@@ -36597,16 +36597,16 @@
         <v>128</v>
       </c>
       <c r="G1296" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1296" s="2">
-        <v>0</v>
+        <v>4.386574074074074E-3</v>
       </c>
       <c r="I1296" s="1">
         <v>46146.724768518521</v>
       </c>
       <c r="J1296">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1296" t="s">
         <v>11</v>
@@ -36684,16 +36684,16 @@
         <v>128</v>
       </c>
       <c r="G1299" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1299" s="2">
-        <v>0</v>
+        <v>5.6712962962962967E-3</v>
       </c>
       <c r="I1299" s="1">
         <v>46146.726157407407</v>
       </c>
       <c r="J1299">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1299" t="s">
         <v>11</v>
@@ -36751,7 +36751,7 @@
         <v>46146.727546296293</v>
       </c>
       <c r="J1301">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1301" t="s">
         <v>11</v>
@@ -36780,7 +36780,7 @@
         <v>46146.727546296293</v>
       </c>
       <c r="J1302">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1302" t="s">
         <v>11</v>
@@ -36829,16 +36829,16 @@
         <v>128</v>
       </c>
       <c r="G1304" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1304" s="2">
-        <v>0</v>
+        <v>5.115740740740741E-3</v>
       </c>
       <c r="I1304" s="1">
         <v>46146.728935185187</v>
       </c>
       <c r="J1304">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1304" t="s">
         <v>11</v>
@@ -37070,7 +37070,7 @@
         <v>46146.732407407406</v>
       </c>
       <c r="J1312">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1312" t="s">
         <v>11</v>
@@ -37090,48 +37090,26 @@
         <v>128</v>
       </c>
       <c r="G1313" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H1313" s="2">
-        <v>0</v>
+        <v>1.1574074074074073E-5</v>
       </c>
       <c r="I1313" s="1">
         <v>46146.733101851853</v>
       </c>
       <c r="J1313">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1313" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1314" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B1314" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1314">
-        <v>1258</v>
-      </c>
-      <c r="D1314" t="s">
-        <v>95</v>
-      </c>
-      <c r="F1314" t="s">
-        <v>128</v>
-      </c>
-      <c r="G1314" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1314" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1314" s="1">
-        <v>46146.710300925923</v>
-      </c>
-      <c r="J1314">
-        <v>2</v>
-      </c>
+      <c r="H1314" s="2"/>
+      <c r="I1314" s="1"/>
       <c r="K1314" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1315" spans="2:11" x14ac:dyDescent="0.3">
@@ -37139,57 +37117,35 @@
         <v>41</v>
       </c>
       <c r="C1315">
-        <v>1266</v>
+        <v>1258</v>
       </c>
       <c r="D1315" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F1315" t="s">
         <v>128</v>
       </c>
       <c r="G1315" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1315" s="2">
-        <v>9.479166666666667E-3</v>
+        <v>3.1250000000000001E-4</v>
       </c>
       <c r="I1315" s="1">
-        <v>46146.710995370369</v>
+        <v>46146.710300925923</v>
       </c>
       <c r="J1315">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1315" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1316" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B1316" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1316">
-        <v>1755</v>
-      </c>
-      <c r="D1316" t="s">
-        <v>98</v>
-      </c>
-      <c r="F1316" t="s">
-        <v>128</v>
-      </c>
-      <c r="G1316" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1316" s="2">
-        <v>5.1736111111111115E-3</v>
-      </c>
-      <c r="I1316" s="1">
-        <v>46146.710995370369</v>
-      </c>
-      <c r="J1316">
-        <v>2</v>
-      </c>
+      <c r="H1316" s="2"/>
+      <c r="I1316" s="1"/>
       <c r="K1316" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1317" spans="2:11" x14ac:dyDescent="0.3">
@@ -37197,10 +37153,10 @@
         <v>41</v>
       </c>
       <c r="C1317">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="D1317" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F1317" t="s">
         <v>128</v>
@@ -37209,10 +37165,10 @@
         <v>10</v>
       </c>
       <c r="H1317" s="2">
-        <v>6.828703703703704E-3</v>
+        <v>9.479166666666667E-3</v>
       </c>
       <c r="I1317" s="1">
-        <v>46146.711689814816</v>
+        <v>46146.710995370369</v>
       </c>
       <c r="J1317">
         <v>0</v>
@@ -37226,44 +37182,94 @@
         <v>41</v>
       </c>
       <c r="C1318">
-        <v>1274</v>
+        <v>1755</v>
       </c>
       <c r="D1318" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="F1318" t="s">
         <v>128</v>
       </c>
       <c r="G1318" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1318" s="2">
+        <v>5.1736111111111115E-3</v>
+      </c>
+      <c r="I1318" s="1">
+        <v>46146.710995370369</v>
+      </c>
+      <c r="J1318">
+        <v>2</v>
+      </c>
+      <c r="K1318" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1319" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B1319" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1319">
+        <v>1267</v>
+      </c>
+      <c r="D1319" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1319" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1319" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1319" s="2">
+        <v>6.828703703703704E-3</v>
+      </c>
+      <c r="I1319" s="1">
+        <v>46146.711689814816</v>
+      </c>
+      <c r="J1319">
+        <v>0</v>
+      </c>
+      <c r="K1319" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1320" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B1320" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1320">
+        <v>1274</v>
+      </c>
+      <c r="D1320" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1320" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1320" t="s">
         <v>14</v>
       </c>
-      <c r="H1318" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1318" s="1">
+      <c r="H1320" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1320" s="1">
         <v>46151.542824074073</v>
       </c>
-      <c r="J1318">
+      <c r="J1320">
         <v>1</v>
       </c>
-      <c r="K1318" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1319" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H1319" s="2"/>
-      <c r="I1319" s="1"/>
-      <c r="K1319" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="1320" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H1320" s="2"/>
-      <c r="I1320" s="1"/>
+      <c r="K1320" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1321" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H1321" s="2"/>
       <c r="I1321" s="1"/>
+      <c r="K1321" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="1322" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H1322" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Voyager - Samsara\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\voyager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{994A50D3-9D57-48D4-A34A-AA8616EE3089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156059C4-BB28-4208-AF37-9BEF9F6C43D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37749,7 +37749,7 @@
         <v>46176.421759259261</v>
       </c>
       <c r="J1333">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1333" t="s">
         <v>11</v>
@@ -37952,7 +37952,7 @@
         <v>46176.423842592594</v>
       </c>
       <c r="J1340">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1340" t="s">
         <v>11</v>
@@ -38048,7 +38048,7 @@
         <v>46176.424537037034</v>
       </c>
       <c r="J1344">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1344" t="s">
         <v>11</v>
@@ -38106,7 +38106,7 @@
         <v>46176.42523148148</v>
       </c>
       <c r="J1346">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1346" t="s">
         <v>11</v>
@@ -38135,7 +38135,7 @@
         <v>46176.42523148148</v>
       </c>
       <c r="J1347">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1347" t="s">
         <v>11</v>
@@ -38155,16 +38155,16 @@
         <v>25</v>
       </c>
       <c r="G1348" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1348" s="2">
-        <v>0</v>
+        <v>8.0092592592592594E-3</v>
       </c>
       <c r="I1348" s="1">
         <v>46176.42523148148</v>
       </c>
       <c r="J1348">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1348" t="s">
         <v>11</v>
@@ -38193,7 +38193,7 @@
         <v>46176.425925925927</v>
       </c>
       <c r="J1349">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1349" t="s">
         <v>11</v>
@@ -38454,16 +38454,16 @@
         <v>25</v>
       </c>
       <c r="G1359" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1359" s="2">
-        <v>0</v>
+        <v>1.1979166666666667E-2</v>
       </c>
       <c r="I1359" s="1">
         <v>46176.428703703707</v>
       </c>
       <c r="J1359">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1359" t="s">
         <v>11</v>
@@ -38570,16 +38570,16 @@
         <v>25</v>
       </c>
       <c r="G1363" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1363" s="2">
-        <v>0</v>
+        <v>8.4027777777777781E-3</v>
       </c>
       <c r="I1363" s="1">
         <v>46176.429398148146</v>
       </c>
       <c r="J1363">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1363" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\voyager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C068E5FF-ED6E-49D8-82D3-C319EEBFF113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4406A47-A9EB-4233-A23D-0FF5498739E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6855" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6852" uniqueCount="134">
   <si>
     <t>Company Name</t>
   </si>
@@ -814,7 +814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -890,7 +890,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>50</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>50</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>50</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>50</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>50</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>50</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>50</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H74" s="2"/>
       <c r="I74" s="1"/>
       <c r="J74" s="2"/>
@@ -3016,7 +3016,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>50</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>50</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>50</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H115" s="2"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -4027,7 +4027,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>50</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>50</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>50</v>
       </c>
@@ -5681,7 +5681,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>50</v>
       </c>
@@ -6185,7 +6185,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -7092,7 +7092,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>50</v>
       </c>
@@ -9490,7 +9490,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>50</v>
       </c>
@@ -9812,7 +9812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>50</v>
       </c>
@@ -9870,7 +9870,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>50</v>
       </c>
@@ -10334,7 +10334,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>50</v>
       </c>
@@ -10392,7 +10392,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>50</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>50</v>
       </c>
@@ -11128,7 +11128,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>50</v>
       </c>
@@ -39702,16 +39702,16 @@
         <v>34</v>
       </c>
       <c r="G1405" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1405" s="2">
-        <v>0</v>
+        <v>7.1990740740740739E-3</v>
       </c>
       <c r="I1405" s="1">
         <v>46237.840162037035</v>
       </c>
       <c r="J1405" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1405" s="1" t="s">
         <v>11</v>
@@ -39847,10 +39847,10 @@
         <v>34</v>
       </c>
       <c r="G1410" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1410" s="2">
-        <v>0</v>
+        <v>5.8101851851851856E-3</v>
       </c>
       <c r="I1410" s="1">
         <v>46237.842245370368</v>
@@ -39943,7 +39943,7 @@
         <v>46237.843634259261</v>
       </c>
       <c r="J1413" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1413" s="1" t="s">
         <v>11</v>
@@ -40021,27 +40021,48 @@
         <v>34</v>
       </c>
       <c r="G1416" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1416" s="2">
-        <v>0</v>
+        <v>6.099537037037037E-3</v>
       </c>
       <c r="I1416" s="1">
         <v>46237.845023148147</v>
       </c>
       <c r="J1416" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1416" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1417" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1417" s="2"/>
-      <c r="I1417" s="1"/>
-      <c r="J1417" s="2"/>
+      <c r="B1417" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1417">
+        <v>1241</v>
+      </c>
+      <c r="D1417" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1417" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1417" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1417" s="2">
+        <v>7.3032407407407404E-3</v>
+      </c>
+      <c r="I1417" s="1">
+        <v>46237.845717592594</v>
+      </c>
+      <c r="J1417" s="2">
+        <v>1</v>
+      </c>
       <c r="K1417" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1418" spans="2:11" x14ac:dyDescent="0.25">
@@ -40049,25 +40070,25 @@
         <v>50</v>
       </c>
       <c r="C1418">
-        <v>1241</v>
+        <v>1252</v>
       </c>
       <c r="D1418" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F1418" t="s">
         <v>34</v>
       </c>
       <c r="G1418" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1418" s="2">
-        <v>0</v>
+        <v>5.5671296296296293E-3</v>
       </c>
       <c r="I1418" s="1">
         <v>46237.845717592594</v>
       </c>
       <c r="J1418" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1418" s="1" t="s">
         <v>11</v>
@@ -40078,25 +40099,25 @@
         <v>50</v>
       </c>
       <c r="C1419">
-        <v>1252</v>
+        <v>1748</v>
       </c>
       <c r="D1419" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F1419" t="s">
         <v>34</v>
       </c>
       <c r="G1419" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1419" s="2">
-        <v>0</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="I1419" s="1">
-        <v>46237.845717592594</v>
+        <v>46237.846412037034</v>
       </c>
       <c r="J1419" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1419" s="1" t="s">
         <v>11</v>
@@ -40107,22 +40128,22 @@
         <v>50</v>
       </c>
       <c r="C1420">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="D1420" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F1420" t="s">
         <v>34</v>
       </c>
       <c r="G1420" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1420" s="2">
-        <v>0</v>
+        <v>1.1539351851851851E-2</v>
       </c>
       <c r="I1420" s="1">
-        <v>46237.846412037034</v>
+        <v>46237.84710648148</v>
       </c>
       <c r="J1420" s="2">
         <v>0</v>
@@ -40132,11 +40153,32 @@
       </c>
     </row>
     <row r="1421" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1421" s="2"/>
-      <c r="I1421" s="1"/>
-      <c r="J1421" s="2"/>
+      <c r="B1421" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1421">
+        <v>5526</v>
+      </c>
+      <c r="D1421" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1421" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1421" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1421" s="2">
+        <v>6.7013888888888887E-3</v>
+      </c>
+      <c r="I1421" s="1">
+        <v>46237.84710648148</v>
+      </c>
+      <c r="J1421" s="2">
+        <v>1</v>
+      </c>
       <c r="K1421" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1422" spans="2:11" x14ac:dyDescent="0.25">
@@ -40144,10 +40186,10 @@
         <v>50</v>
       </c>
       <c r="C1422">
-        <v>1749</v>
+        <v>1754</v>
       </c>
       <c r="D1422" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F1422" t="s">
         <v>34</v>
@@ -40156,10 +40198,10 @@
         <v>10</v>
       </c>
       <c r="H1422" s="2">
-        <v>1.1539351851851851E-2</v>
+        <v>1.224537037037037E-2</v>
       </c>
       <c r="I1422" s="1">
-        <v>46237.84710648148</v>
+        <v>46237.847800925927</v>
       </c>
       <c r="J1422" s="2">
         <v>0</v>
@@ -40173,57 +40215,36 @@
         <v>50</v>
       </c>
       <c r="C1423">
-        <v>5526</v>
+        <v>3168</v>
       </c>
       <c r="D1423" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="F1423" t="s">
         <v>34</v>
       </c>
       <c r="G1423" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H1423" s="2">
-        <v>0</v>
+        <v>1.3888888888888889E-4</v>
       </c>
       <c r="I1423" s="1">
-        <v>46237.84710648148</v>
+        <v>46237.848495370374</v>
       </c>
       <c r="J1423" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1423" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1424" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1424" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1424">
-        <v>1754</v>
-      </c>
-      <c r="D1424" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1424" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1424" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1424" s="2">
-        <v>1.224537037037037E-2</v>
-      </c>
-      <c r="I1424" s="1">
-        <v>46237.847800925927</v>
-      </c>
-      <c r="J1424" s="2">
-        <v>0</v>
-      </c>
+      <c r="H1424" s="2"/>
+      <c r="I1424" s="1"/>
+      <c r="J1424" s="2"/>
       <c r="K1424" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1425" spans="2:11" x14ac:dyDescent="0.25">
@@ -40231,36 +40252,57 @@
         <v>50</v>
       </c>
       <c r="C1425">
-        <v>3168</v>
+        <v>1249</v>
       </c>
       <c r="D1425" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="F1425" t="s">
         <v>34</v>
       </c>
       <c r="G1425" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H1425" s="2">
-        <v>1.3888888888888889E-4</v>
+        <v>0</v>
       </c>
       <c r="I1425" s="1">
         <v>46237.848495370374</v>
       </c>
       <c r="J1425" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1425" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1426" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1426" s="2"/>
-      <c r="I1426" s="1"/>
-      <c r="J1426" s="2"/>
+      <c r="B1426" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1426">
+        <v>1265</v>
+      </c>
+      <c r="D1426" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1426" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1426" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1426" s="2">
+        <v>7.7199074074074071E-3</v>
+      </c>
+      <c r="I1426" s="1">
+        <v>46237.849189814813</v>
+      </c>
+      <c r="J1426" s="2">
+        <v>0</v>
+      </c>
       <c r="K1426" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1427" spans="2:11" x14ac:dyDescent="0.25">
@@ -40268,22 +40310,22 @@
         <v>50</v>
       </c>
       <c r="C1427">
-        <v>1249</v>
+        <v>5046</v>
       </c>
       <c r="D1427" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="F1427" t="s">
         <v>34</v>
       </c>
       <c r="G1427" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1427" s="2">
-        <v>0</v>
+        <v>6.4814814814814813E-3</v>
       </c>
       <c r="I1427" s="1">
-        <v>46237.848495370374</v>
+        <v>46237.849189814813</v>
       </c>
       <c r="J1427" s="2">
         <v>0</v>
@@ -40297,10 +40339,10 @@
         <v>50</v>
       </c>
       <c r="C1428">
-        <v>1265</v>
+        <v>5209</v>
       </c>
       <c r="D1428" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="F1428" t="s">
         <v>34</v>
@@ -40309,10 +40351,10 @@
         <v>10</v>
       </c>
       <c r="H1428" s="2">
-        <v>7.7199074074074071E-3</v>
+        <v>7.4421296296296293E-3</v>
       </c>
       <c r="I1428" s="1">
-        <v>46237.849189814813</v>
+        <v>46237.84988425926</v>
       </c>
       <c r="J1428" s="2">
         <v>0</v>
@@ -40326,10 +40368,10 @@
         <v>50</v>
       </c>
       <c r="C1429">
-        <v>5046</v>
+        <v>3195</v>
       </c>
       <c r="D1429" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="F1429" t="s">
         <v>34</v>
@@ -40338,13 +40380,13 @@
         <v>10</v>
       </c>
       <c r="H1429" s="2">
-        <v>6.4814814814814813E-3</v>
+        <v>6.7708333333333336E-3</v>
       </c>
       <c r="I1429" s="1">
-        <v>46237.849189814813</v>
+        <v>46237.850578703707</v>
       </c>
       <c r="J1429" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1429" s="1" t="s">
         <v>11</v>
@@ -40355,25 +40397,25 @@
         <v>50</v>
       </c>
       <c r="C1430">
-        <v>5209</v>
+        <v>1263</v>
       </c>
       <c r="D1430" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="F1430" t="s">
         <v>34</v>
       </c>
       <c r="G1430" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1430" s="2">
-        <v>7.4421296296296293E-3</v>
+        <v>0</v>
       </c>
       <c r="I1430" s="1">
-        <v>46237.84988425926</v>
+        <v>46237.850578703707</v>
       </c>
       <c r="J1430" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1430" s="1" t="s">
         <v>11</v>
@@ -40384,22 +40426,22 @@
         <v>50</v>
       </c>
       <c r="C1431">
-        <v>3195</v>
+        <v>1245</v>
       </c>
       <c r="D1431" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="F1431" t="s">
         <v>34</v>
       </c>
       <c r="G1431" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1431" s="2">
-        <v>9.2592592592592588E-5</v>
+        <v>6.9791666666666665E-3</v>
       </c>
       <c r="I1431" s="1">
-        <v>46237.850578703707</v>
+        <v>46237.851273148146</v>
       </c>
       <c r="J1431" s="2">
         <v>0</v>
@@ -40409,11 +40451,32 @@
       </c>
     </row>
     <row r="1432" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1432" s="2"/>
-      <c r="I1432" s="1"/>
-      <c r="J1432" s="2"/>
+      <c r="B1432" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1432">
+        <v>1248</v>
+      </c>
+      <c r="D1432" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1432" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1432" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1432" s="2">
+        <v>1.050925925925926E-2</v>
+      </c>
+      <c r="I1432" s="1">
+        <v>46237.851967592593</v>
+      </c>
+      <c r="J1432" s="2">
+        <v>0</v>
+      </c>
       <c r="K1432" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1433" spans="2:11" x14ac:dyDescent="0.25">
@@ -40421,25 +40484,25 @@
         <v>50</v>
       </c>
       <c r="C1433">
-        <v>1263</v>
+        <v>1275</v>
       </c>
       <c r="D1433" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F1433" t="s">
         <v>34</v>
       </c>
       <c r="G1433" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1433" s="2">
-        <v>0</v>
+        <v>6.4467592592592588E-3</v>
       </c>
       <c r="I1433" s="1">
-        <v>46237.850578703707</v>
+        <v>46237.851967592593</v>
       </c>
       <c r="J1433" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1433" s="1" t="s">
         <v>11</v>
@@ -40450,10 +40513,10 @@
         <v>50</v>
       </c>
       <c r="C1434">
-        <v>1245</v>
+        <v>1761</v>
       </c>
       <c r="D1434" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F1434" t="s">
         <v>34</v>
@@ -40462,10 +40525,10 @@
         <v>10</v>
       </c>
       <c r="H1434" s="2">
-        <v>6.9791666666666665E-3</v>
+        <v>6.3078703703703708E-3</v>
       </c>
       <c r="I1434" s="1">
-        <v>46237.851273148146</v>
+        <v>46237.852662037039</v>
       </c>
       <c r="J1434" s="2">
         <v>0</v>
@@ -40479,10 +40542,10 @@
         <v>50</v>
       </c>
       <c r="C1435">
-        <v>1248</v>
+        <v>2001</v>
       </c>
       <c r="D1435" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="F1435" t="s">
         <v>34</v>
@@ -40491,13 +40554,13 @@
         <v>10</v>
       </c>
       <c r="H1435" s="2">
-        <v>1.050925925925926E-2</v>
+        <v>6.3194444444444444E-3</v>
       </c>
       <c r="I1435" s="1">
-        <v>46237.851967592593</v>
+        <v>46237.853356481479</v>
       </c>
       <c r="J1435" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1435" s="1" t="s">
         <v>11</v>
@@ -40508,22 +40571,22 @@
         <v>50</v>
       </c>
       <c r="C1436">
-        <v>1275</v>
+        <v>2000</v>
       </c>
       <c r="D1436" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="F1436" t="s">
         <v>34</v>
       </c>
       <c r="G1436" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1436" s="2">
-        <v>0</v>
+        <v>7.0254629629629634E-3</v>
       </c>
       <c r="I1436" s="1">
-        <v>46237.851967592593</v>
+        <v>46237.853356481479</v>
       </c>
       <c r="J1436" s="2">
         <v>0</v>
@@ -40537,10 +40600,10 @@
         <v>50</v>
       </c>
       <c r="C1437">
-        <v>1761</v>
+        <v>1258</v>
       </c>
       <c r="D1437" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F1437" t="s">
         <v>34</v>
@@ -40549,13 +40612,13 @@
         <v>10</v>
       </c>
       <c r="H1437" s="2">
-        <v>6.3078703703703708E-3</v>
+        <v>1.7280092592592593E-2</v>
       </c>
       <c r="I1437" s="1">
-        <v>46237.852662037039</v>
+        <v>46237.854050925926</v>
       </c>
       <c r="J1437" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1437" s="1" t="s">
         <v>11</v>
@@ -40566,22 +40629,22 @@
         <v>50</v>
       </c>
       <c r="C1438">
-        <v>2001</v>
+        <v>1266</v>
       </c>
       <c r="D1438" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F1438" t="s">
         <v>34</v>
       </c>
       <c r="G1438" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1438" s="2">
-        <v>0</v>
+        <v>1.40625E-2</v>
       </c>
       <c r="I1438" s="1">
-        <v>46237.853356481479</v>
+        <v>46237.854745370372</v>
       </c>
       <c r="J1438" s="2">
         <v>0</v>
@@ -40595,25 +40658,25 @@
         <v>50</v>
       </c>
       <c r="C1439">
-        <v>2000</v>
+        <v>1755</v>
       </c>
       <c r="D1439" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F1439" t="s">
         <v>34</v>
       </c>
       <c r="G1439" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1439" s="2">
-        <v>7.0254629629629634E-3</v>
+        <v>0</v>
       </c>
       <c r="I1439" s="1">
-        <v>46237.853356481479</v>
+        <v>46237.854745370372</v>
       </c>
       <c r="J1439" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1439" s="1" t="s">
         <v>11</v>
@@ -40624,22 +40687,22 @@
         <v>50</v>
       </c>
       <c r="C1440">
-        <v>1258</v>
+        <v>1267</v>
       </c>
       <c r="D1440" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F1440" t="s">
         <v>34</v>
       </c>
       <c r="G1440" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1440" s="2">
-        <v>0</v>
+        <v>9.0856481481481483E-3</v>
       </c>
       <c r="I1440" s="1">
-        <v>46237.854050925926</v>
+        <v>46237.855439814812</v>
       </c>
       <c r="J1440" s="2">
         <v>0</v>
@@ -40648,165 +40711,96 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1441" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1441" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1441">
-        <v>1266</v>
-      </c>
-      <c r="D1441" t="s">
-        <v>105</v>
-      </c>
-      <c r="F1441" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1441" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1441" s="2">
-        <v>1.40625E-2</v>
-      </c>
-      <c r="I1441" s="1">
-        <v>46237.854745370372</v>
-      </c>
-      <c r="J1441" s="2">
-        <v>0</v>
-      </c>
-      <c r="K1441" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1442" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1442" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1442">
-        <v>1755</v>
-      </c>
-      <c r="D1442" t="s">
-        <v>106</v>
-      </c>
-      <c r="F1442" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1442" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1442" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1442" s="1">
-        <v>46237.854745370372</v>
-      </c>
-      <c r="J1442" s="2">
-        <v>0</v>
-      </c>
-      <c r="K1442" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1443" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1443" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1443">
-        <v>1267</v>
-      </c>
-      <c r="D1443" t="s">
-        <v>107</v>
-      </c>
-      <c r="F1443" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1443" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1443" s="2">
-        <v>9.0856481481481483E-3</v>
-      </c>
-      <c r="I1443" s="1">
-        <v>46237.855439814812</v>
-      </c>
-      <c r="J1443" s="2">
-        <v>0</v>
-      </c>
-      <c r="K1443" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1444" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1441" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1441" s="2"/>
+      <c r="I1441" s="1"/>
+      <c r="J1441" s="2"/>
+      <c r="K1441" s="1"/>
+    </row>
+    <row r="1442" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1442" s="2"/>
+      <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
+      <c r="K1442" s="1"/>
+    </row>
+    <row r="1443" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1443" s="2"/>
+      <c r="I1443" s="1"/>
+      <c r="J1443" s="2"/>
+      <c r="K1443" s="1"/>
+    </row>
+    <row r="1444" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H1444" s="2"/>
       <c r="I1444" s="1"/>
       <c r="J1444" s="2"/>
       <c r="K1444" s="1"/>
     </row>
-    <row r="1445" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1445" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H1445" s="2"/>
       <c r="I1445" s="1"/>
       <c r="J1445" s="2"/>
       <c r="K1445" s="1"/>
     </row>
-    <row r="1446" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1446" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H1446" s="2"/>
       <c r="I1446" s="1"/>
       <c r="J1446" s="2"/>
       <c r="K1446" s="1"/>
     </row>
-    <row r="1447" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1447" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H1447" s="2"/>
       <c r="I1447" s="1"/>
       <c r="J1447" s="2"/>
       <c r="K1447" s="1"/>
     </row>
-    <row r="1448" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1448" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H1448" s="2"/>
       <c r="I1448" s="1"/>
       <c r="K1448" s="1"/>
     </row>
-    <row r="1449" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1449" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H1449" s="2"/>
       <c r="I1449" s="1"/>
       <c r="J1449" s="2"/>
       <c r="K1449" s="1"/>
     </row>
-    <row r="1450" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1450" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H1450" s="2"/>
       <c r="I1450" s="1"/>
       <c r="J1450" s="2"/>
       <c r="K1450" s="1"/>
     </row>
-    <row r="1451" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1451" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H1451" s="2"/>
       <c r="I1451" s="1"/>
       <c r="J1451" s="2"/>
       <c r="K1451" s="1"/>
     </row>
-    <row r="1452" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1452" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H1452" s="2"/>
       <c r="I1452" s="1"/>
       <c r="J1452" s="2"/>
       <c r="K1452" s="1"/>
     </row>
-    <row r="1453" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1453" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H1453" s="2"/>
       <c r="I1453" s="1"/>
       <c r="J1453" s="2"/>
       <c r="K1453" s="1"/>
     </row>
-    <row r="1454" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1454" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H1454" s="2"/>
       <c r="I1454" s="1"/>
       <c r="J1454" s="2"/>
       <c r="K1454" s="1"/>
     </row>
-    <row r="1455" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1455" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H1455" s="2"/>
       <c r="I1455" s="1"/>
       <c r="J1455" s="2"/>
       <c r="K1455" s="1"/>
     </row>
-    <row r="1456" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1456" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H1456" s="2"/>
       <c r="I1456" s="1"/>
       <c r="J1456" s="2"/>
@@ -43793,6 +43787,7 @@
       <c r="K1957" s="1"/>
     </row>
     <row r="1958" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1958" s="2"/>
       <c r="I1958" s="1"/>
       <c r="K1958" s="1"/>
     </row>
@@ -43830,6 +43825,7 @@
       <c r="K1964" s="1"/>
     </row>
     <row r="1965" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1965" s="2"/>
       <c r="I1965" s="1"/>
       <c r="K1965" s="1"/>
     </row>
@@ -43894,6 +43890,7 @@
       <c r="K1976" s="1"/>
     </row>
     <row r="1977" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1977" s="2"/>
       <c r="I1977" s="1"/>
     </row>
     <row r="1978" spans="8:11" x14ac:dyDescent="0.25">
@@ -43925,11 +43922,11 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
     <row r="1984" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1984" s="2"/>
       <c r="I1984" s="1"/>
       <c r="K1984" s="1"/>
     </row>
@@ -43940,6 +43937,7 @@
       <c r="K1985" s="1"/>
     </row>
     <row r="1986" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1986" s="2"/>
       <c r="I1986" s="1"/>
       <c r="K1986" s="1"/>
     </row>
@@ -44015,6 +44013,7 @@
       <c r="K1999" s="1"/>
     </row>
     <row r="2000" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2000" s="2"/>
       <c r="I2000" s="1"/>
       <c r="K2000" s="1"/>
     </row>
@@ -44025,6 +44024,7 @@
       <c r="K2001" s="1"/>
     </row>
     <row r="2002" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2002" s="2"/>
       <c r="I2002" s="1"/>
     </row>
     <row r="2003" spans="8:11" x14ac:dyDescent="0.25">
@@ -44056,7 +44056,6 @@
       <c r="K2007" s="1"/>
     </row>
     <row r="2008" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H2008" s="2"/>
       <c r="I2008" s="1"/>
       <c r="K2008" s="1"/>
     </row>
@@ -73349,6 +73348,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -73641,6 +73641,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -73951,6 +73953,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -74075,6 +74078,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -74086,6 +74090,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -74234,6 +74239,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -74244,10 +74250,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -74281,15 +74289,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -74330,18 +74341,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -74357,6 +74372,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -74366,10 +74382,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -74405,10 +74423,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -74434,6 +74454,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -74448,6 +74469,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -74482,6 +74504,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -74491,6 +74514,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -74500,6 +74524,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -74514,15 +74539,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -74552,6 +74578,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -74572,11 +74599,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -74585,6 +74614,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -74614,6 +74644,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -74623,10 +74654,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -74641,14 +74674,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -74668,10 +74704,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -74691,9 +74729,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -74728,18 +74769,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -74754,12 +74799,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -74774,10 +74819,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -74797,6 +74844,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -74816,6 +74864,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -74825,6 +74874,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -74870,6 +74920,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -74879,6 +74930,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -74893,6 +74945,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -74902,10 +74955,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -74920,6 +74975,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -74929,6 +74985,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -74948,6 +75005,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -74967,10 +75025,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -74980,6 +75040,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -74990,10 +75051,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -75008,18 +75071,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -75039,10 +75106,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -75062,6 +75131,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -75092,7 +75162,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -75107,10 +75176,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -75125,6 +75196,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -75139,11 +75211,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -75153,6 +75225,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -75168,6 +75241,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -75182,6 +75256,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -75202,6 +75277,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -75227,11 +75303,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -75250,15 +75328,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -75268,6 +75347,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -75287,6 +75367,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -75301,6 +75382,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -75320,10 +75402,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -75333,6 +75417,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -75343,6 +75428,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -75379,7 +75465,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -75388,6 +75473,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -75401,10 +75487,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
